--- a/src/assets/downloads/Latvia-TestScenario4-AnnualProgressReport2026-2028.xlsx.xlsx
+++ b/src/assets/downloads/Latvia-TestScenario4-AnnualProgressReport2026-2028.xlsx.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef7a825b9bce984a/Documents/Consulting/Phase II - Latvia/Model/Finals - Website versions/Inputs/Latvia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef7a825b9bce984a/Documents/Claude/Projects/FISCO/fisco-site/src/assets/downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="8_{5FF61014-9E2A-4B3F-B017-79FAC56A8DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDE5FA5D-5F9D-4D30-A2AC-F372F609027D}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="8_{5FF61014-9E2A-4B3F-B017-79FAC56A8DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F3603E3-8D2C-409D-8811-AE363C021007}"/>
   <bookViews>
-    <workbookView xWindow="-32490" yWindow="-1815" windowWidth="29010" windowHeight="15105" xr2:uid="{8FD35C3B-BB10-4593-87EA-7C211D5C60DD}"/>
+    <workbookView xWindow="-67320" yWindow="-3945" windowWidth="29040" windowHeight="15720" xr2:uid="{8FD35C3B-BB10-4593-87EA-7C211D5C60DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2283,16 +2283,16 @@
         <v>1</v>
       </c>
       <c r="E56" s="15">
-        <v>18.600000000000001</v>
+        <v>2.9976595002552808</v>
       </c>
       <c r="F56" s="15">
-        <v>7.7</v>
+        <v>3.1420657625767783</v>
       </c>
       <c r="G56" s="15">
-        <v>16.399999999999999</v>
+        <v>3.4555754586740171</v>
       </c>
       <c r="H56" s="15">
-        <v>45.1</v>
+        <v>4.7257681343411875</v>
       </c>
       <c r="I56" s="15"/>
     </row>
@@ -2309,18 +2309,10 @@
       <c r="D57" s="15">
         <v>0.3</v>
       </c>
-      <c r="E57" s="15">
-        <v>91.1</v>
-      </c>
-      <c r="F57" s="15">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="G57" s="15">
-        <v>34</v>
-      </c>
-      <c r="H57" s="15">
-        <v>59</v>
-      </c>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
       <c r="I57" s="15"/>
     </row>
     <row r="59" spans="1:9" ht="19.5" x14ac:dyDescent="0.6">
